--- a/chaingraph/exporters/sample-export.xlsx
+++ b/chaingraph/exporters/sample-export.xlsx
@@ -147,6 +147,14 @@
         </is>
       </c>
     </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not legal, investment, tax, or compliance advice. A computed view of the cited authority as of generated_at, not a substitute for review by a qualified advisor against the current official source text.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
